--- a/slide_classification/TCGA_Results/Averaging/UNI2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Averaging/UNI2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="baseline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -578,26 +579,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[[83  5]
- [ 5 10]]</t>
+          <t>[[83, 5], [5, 10]]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[[82  2]
- [ 8  5]]</t>
+          <t>[[82, 2], [8, 5]]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[[88  4]
- [ 6 14]]</t>
+          <t>[[88, 4], [6, 14]]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>[[86  3]
- [ 8  4]]</t>
+          <t>[[86, 3], [8, 4]]</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -613,7 +610,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8446601941747572</v>
+        <v>0.8349514563106796</v>
       </c>
       <c r="C8" t="n">
         <v>0.8350515463917526</v>
@@ -622,10 +619,10 @@
         <v>0.8214285714285714</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8316831683168316</v>
+        <v>0.801980198019802</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8332058700779782</v>
+        <v>0.8233529430377013</v>
       </c>
     </row>
     <row r="9">
@@ -635,19 +632,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8261363636363637</v>
+        <v>0.7928030303030302</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7422161172161172</v>
+        <v>0.7747252747252746</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7934782608695652</v>
+        <v>0.8521739130434782</v>
       </c>
       <c r="E9" t="n">
-        <v>0.724250936329588</v>
+        <v>0.7073970037453183</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7715204195129085</v>
+        <v>0.7817748054542752</v>
       </c>
     </row>
     <row r="10">
@@ -657,19 +654,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7518072289156627</v>
+        <v>0.7311530784584677</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7006172839506173</v>
+        <v>0.7147058823529412</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7425287356321839</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6760988492737219</v>
+        <v>0.6463585434173669</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7177630244430464</v>
+        <v>0.7135305665333844</v>
       </c>
     </row>
     <row r="11">
@@ -679,19 +676,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8593987600888994</v>
+        <v>0.8495481031961469</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8474608629247805</v>
+        <v>0.8503335354760463</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8341543513957308</v>
+        <v>0.83843537414966</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8472416002211426</v>
+        <v>0.825207310647031</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8470638936576382</v>
+        <v>0.840881080867221</v>
       </c>
     </row>
     <row r="12">
@@ -701,19 +698,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8810606060606061</v>
+        <v>0.8803030303030303</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8388278388278388</v>
+        <v>0.8580586080586081</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9032608695652173</v>
+        <v>0.9016304347826086</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7883895131086143</v>
+        <v>0.8071161048689138</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8528847068905691</v>
+        <v>0.8617770445032902</v>
       </c>
     </row>
     <row r="13">
@@ -724,31 +721,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[[75 13]
- [ 3 12]]</t>
+          <t>[[75, 13], [4, 11]]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[[73 11]
- [ 5  8]]</t>
+          <t>[[72, 12], [4, 9]]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[[77 15]
- [ 5 15]]</t>
+          <t>[[74, 18], [2, 18]]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[[77 12]
- [ 5  7]]</t>
+          <t>[[74, 15], [5, 7]]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[76, 13], [4, 10]]</t>
+          <t>[[74, 14], [4, 11]]</t>
         </is>
       </c>
     </row>
@@ -790,10 +783,10 @@
         <v>0.5728260869565217</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.6137640449438202</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5699454078530165</v>
+        <v>0.5879697524223049</v>
       </c>
     </row>
     <row r="16">
@@ -812,10 +805,10 @@
         <v>0.5840848806366048</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5478225478225478</v>
+        <v>0.6467408585055644</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5865837354609871</v>
+        <v>0.6113133131317412</v>
       </c>
     </row>
     <row r="17">
@@ -834,10 +827,10 @@
         <v>0.7822281167108754</v>
       </c>
       <c r="E17" t="n">
-        <v>0.848180788774848</v>
+        <v>0.8707267547104471</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8281189669536608</v>
+        <v>0.8337554584375606</v>
       </c>
     </row>
     <row r="18">
@@ -856,10 +849,10 @@
         <v>0.6951086956521739</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7560861423220975</v>
+        <v>0.7162921348314606</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7133460787909371</v>
+        <v>0.7033975769182779</v>
       </c>
     </row>
     <row r="19">
@@ -870,31 +863,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[[87  1]
- [12  3]]</t>
+          <t>[[87, 1], [12, 3]]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[[83  1]
- [11  2]]</t>
+          <t>[[83, 1], [11, 2]]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[[87  5]
- [16  4]]</t>
+          <t>[[87, 5], [16, 4]]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[[89  0]
- [11  1]]</t>
+          <t>[[87, 2], [9, 3]]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[[86, 2], [12, 2]]</t>
+          <t>[[86, 2], [12, 3]]</t>
         </is>
       </c>
     </row>
@@ -1016,26 +1005,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[[53 35]
- [ 5 10]]</t>
+          <t>[[53, 35], [5, 10]]</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[[47 37]
- [ 6  7]]</t>
+          <t>[[47, 37], [6, 7]]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[[73 19]
- [ 3 17]]</t>
+          <t>[[73, 19], [3, 17]]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>[[52 37]
- [ 4  8]]</t>
+          <t>[[52, 37], [4, 8]]</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1051,19 +1036,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9320388349514563</v>
+        <v>0.912621359223301</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8762886597938144</v>
+        <v>0.865979381443299</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8660714285714286</v>
       </c>
       <c r="E26" t="n">
-        <v>0.900990099009901</v>
+        <v>0.9207920792079208</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8916151127245072</v>
+        <v>0.8913660621114874</v>
       </c>
     </row>
     <row r="27">
@@ -1073,19 +1058,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7943181818181818</v>
+        <v>0.7553030303030304</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5709706959706959</v>
+        <v>0.5325091575091575</v>
       </c>
       <c r="D27" t="n">
-        <v>0.658695652173913</v>
+        <v>0.6641304347826087</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6193820224719101</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6608416381086751</v>
+        <v>0.6546523223153657</v>
       </c>
     </row>
     <row r="28">
@@ -1095,19 +1080,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8406629834254143</v>
+        <v>0.7951381215469613</v>
       </c>
       <c r="C28" t="n">
-        <v>0.5912921348314606</v>
+        <v>0.5303538175046555</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6920962199312715</v>
+        <v>0.7029177718832892</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6606182795698925</v>
+        <v>0.728494623655914</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6961674044395098</v>
+        <v>0.689226083647705</v>
       </c>
     </row>
     <row r="29">
@@ -1117,19 +1102,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9261814085715817</v>
+        <v>0.9050903824491765</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8411039036256226</v>
+        <v>0.8209564399393345</v>
       </c>
       <c r="D29" t="n">
-        <v>0.8370152184585173</v>
+        <v>0.8444486547934825</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8783668689449591</v>
+        <v>0.9026934951559672</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8706668499001702</v>
+        <v>0.8682972430844902</v>
       </c>
     </row>
     <row r="30">
@@ -1139,19 +1124,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9151515151515152</v>
+        <v>0.8909090909090909</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8397435897435896</v>
+        <v>0.8397435897435898</v>
       </c>
       <c r="D30" t="n">
-        <v>0.8521739130434782</v>
+        <v>0.8581521739130434</v>
       </c>
       <c r="E30" t="n">
-        <v>0.7640449438202248</v>
+        <v>0.7687265917602997</v>
       </c>
       <c r="F30" t="n">
-        <v>0.842778490439702</v>
+        <v>0.839382861581506</v>
       </c>
     </row>
     <row r="31">
@@ -1162,31 +1147,413 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[[87  1]
- [ 6  9]]</t>
+          <t>[[86, 2], [7, 8]]</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[[83  1]
- [11  2]]</t>
+          <t>[[83, 1], [12, 1]]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[[89  3]
- [13  7]]</t>
+          <t>[[90, 2], [13, 7]]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>[[88  1]
- [ 9  3]]</t>
+          <t>[[89, 0], [8, 4]]</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[[87, 2], [10, 5]]</t>
+          <t>[[87, 1], [10, 5]]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Classifier</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>N_folds</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>N_test</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>acc</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>acc_sd</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>bacc</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>bacc_sd</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_sd</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>weighted_f1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>weighted_f1_sd</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>auroc</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>auroc_sd</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>conf_matrix</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Averaging</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>UNI2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>413</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9004058081198113</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.007273064183011999</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.7408501941186968</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.07695420824890384</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.7620499033556341</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.06417796770595897</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.8933061641742003</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.01286697564976015</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.8607858357446169</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.05613758985540405</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>[[85, 4], [7, 8]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Averaging</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>UNI2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ann</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="n">
+        <v>413</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.8233529430377013</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.01352664284171277</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.7817748054542752</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.05162220782576746</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.7135305665333844</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0423204376192886</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.840881080867221</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.01019944518645059</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.8617770445032902</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.03511819314085621</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>[[74, 14], [4, 11]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Averaging</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>UNI2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>knn</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>413</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8634160441179239</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.03013092572510507</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5879697524223049</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.01749247414221668</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.6113133131317412</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.02518485317964241</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.8337554584375606</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.03212433984453511</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.7033975769182779</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.02762173516523331</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>[[86, 2], [12, 3]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Averaging</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>UNI2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>proto</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>413</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.6414955877191877</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.0956551312285118</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.6576674165477903</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.1003800938612372</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5581549703036783</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.106310857553062</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.6958965292661974</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.07478317741841735</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.7208858674097438</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.1051291167645182</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>[[56, 32], [4, 10]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Averaging</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>UNI2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>413</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.8913660621114874</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.02550480434518908</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.6546523223153657</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.0795042401596104</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.689226083647705</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.09770777512884811</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.8682972430844902</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.03656071685147935</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.839382861581506</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.04472045947877689</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>[[87, 1], [10, 5]]</t>
         </is>
       </c>
     </row>

--- a/slide_classification/TCGA_Results/Averaging/UNI2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Averaging/UNI2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -610,19 +610,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8349514563106796</v>
+        <v>0.8155339805825242</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8350515463917526</v>
+        <v>0.8762886597938144</v>
       </c>
       <c r="D8" t="n">
         <v>0.8214285714285714</v>
       </c>
       <c r="E8" t="n">
-        <v>0.801980198019802</v>
+        <v>0.8217821782178217</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8233529430377013</v>
+        <v>0.8337583475056829</v>
       </c>
     </row>
     <row r="9">
@@ -632,19 +632,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7928030303030302</v>
+        <v>0.7537878787878788</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7747252747252746</v>
+        <v>0.8310439560439561</v>
       </c>
       <c r="D9" t="n">
         <v>0.8521739130434782</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7073970037453183</v>
+        <v>0.7186329588014981</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7817748054542752</v>
+        <v>0.7889096766692028</v>
       </c>
     </row>
     <row r="10">
@@ -654,19 +654,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7311530784584677</v>
+        <v>0.6995240288653461</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7147058823529412</v>
+        <v>0.775462962962963</v>
       </c>
       <c r="D10" t="n">
         <v>0.7619047619047619</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6463585434173669</v>
+        <v>0.6658088235294117</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7135305665333844</v>
+        <v>0.7256751443156206</v>
       </c>
     </row>
     <row r="11">
@@ -676,19 +676,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8495481031961469</v>
+        <v>0.8318478800427523</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8503335354760463</v>
+        <v>0.8855956471935853</v>
       </c>
       <c r="D11" t="n">
         <v>0.83843537414966</v>
       </c>
       <c r="E11" t="n">
-        <v>0.825207310647031</v>
+        <v>0.8398660454280722</v>
       </c>
       <c r="F11" t="n">
-        <v>0.840881080867221</v>
+        <v>0.8489362367035175</v>
       </c>
     </row>
     <row r="12">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8803030303030303</v>
+        <v>0.8893939393939394</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8580586080586081</v>
+        <v>0.8727106227106228</v>
       </c>
       <c r="D12" t="n">
         <v>0.9016304347826086</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8071161048689138</v>
+        <v>0.7921348314606741</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8617770445032902</v>
+        <v>0.8639674570869612</v>
       </c>
     </row>
     <row r="13">
@@ -721,12 +721,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[[75, 13], [4, 11]]</t>
+          <t>[[74, 14], [5, 10]]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[[72, 12], [4, 9]]</t>
+          <t>[[75, 9], [3, 10]]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[[74, 15], [5, 7]]</t>
+          <t>[[76, 13], [5, 7]]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[74, 14], [4, 11]]</t>
+          <t>[[75, 14], [4, 11]]</t>
         </is>
       </c>
     </row>
@@ -1348,38 +1348,38 @@
         <v>413</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8233529430377013</v>
+        <v>0.8337583475056829</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01352664284171277</v>
+        <v>0.02467998694286086</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7817748054542752</v>
+        <v>0.7889096766692028</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05162220782576746</v>
+        <v>0.05465807091163091</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7135305665333844</v>
+        <v>0.7256751443156206</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0423204376192886</v>
+        <v>0.0448867165208342</v>
       </c>
       <c r="L3" t="n">
-        <v>0.840881080867221</v>
+        <v>0.8489362367035175</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01019944518645059</v>
+        <v>0.02138025254173218</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8617770445032902</v>
+        <v>0.8639674570869612</v>
       </c>
       <c r="O3" t="n">
-        <v>0.03511819314085621</v>
+        <v>0.04272404165367261</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[[74, 14], [4, 11]]</t>
+          <t>[[75, 14], [4, 11]]</t>
         </is>
       </c>
     </row>
